--- a/九龙-将军澳-Park Seasons/Park Seasons_销控明细表.xlsx
+++ b/九龙-将军澳-Park Seasons/Park Seasons_销控明细表.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -21570,7 +21570,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -21912,7 +21912,7 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -43447,20 +43447,20 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 437呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>B | 496呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -43471,12 +43471,12 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>D | 436呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -43487,12 +43487,12 @@
 (26年-06月-23日)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>F | 481呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr"/>
@@ -46633,44 +46633,44 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 537呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>B | 315呎 (1房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>C | 451呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>E | 324呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -46681,12 +46681,12 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 451呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
